--- a/aq_files/0654.xlsx
+++ b/aq_files/0654.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,39 +444,34 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Difficulty</t>
+          <t>Question Type</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ETL stands for:</t>
+          <t>Series is:</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Extract Transfer Load</t>
+          <t>1D</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Extract Transform Load</t>
+          <t>2D</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Evaluate Transform Load</t>
+          <t>3D</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -486,165 +481,145 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Easy</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Unstructured data example:</t>
+          <t>DataFrame is:</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>1D</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Image</t>
+          <t>2D</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Row</t>
+          <t>3D</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Column</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Easy</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Extract phase does:</t>
+          <t>Index defines:</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cleaning</t>
+          <t>Position labels</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Collecting data</t>
+          <t>Values</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Storing</t>
+          <t>Shape</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Analyzing</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Easy</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Transform phase does:</t>
+          <t>Columns represent:</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Rows</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Clean/convert</t>
+          <t>Fields</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Extract</t>
+          <t>Values</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Delete</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Easy</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Load phase does:</t>
+          <t>iloc is:</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Analyze</t>
+          <t>Label-based</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Store data</t>
+          <t>Index-based</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Clean</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -654,39 +629,34 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Easy</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NLP is used for:</t>
+          <t>loc is:</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Images</t>
+          <t>Index-based</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Text processing</t>
+          <t>Label-based</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Audio</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -696,39 +666,34 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Easy</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Parsing means:</t>
+          <t>shape returns:</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cleaning</t>
+          <t>Rows</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Structuring</t>
+          <t>Columns</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Deleting</t>
+          <t>(rows,cols)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -738,39 +703,34 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Batch ETL processes:</t>
+          <t>value_counts():</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Real-time</t>
+          <t>Unique counts</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Large chunks</t>
+          <t>All values</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Small data</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -780,39 +740,34 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Easy</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Streaming ETL processes:</t>
+          <t>describe():</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Batch</t>
+          <t>Stats</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Real-time</t>
+          <t>Values</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Index</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -822,39 +777,34 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Easy</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data validation ensures:</t>
+          <t>columns accessed by:</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Speed</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Accuracy</t>
+          <t>()</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -864,39 +814,34 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Easy</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Schema inference is:</t>
+          <t>dtype means:</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Auto-detection</t>
+          <t>Shape</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Deletion</t>
+          <t>Index</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -906,39 +851,34 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Transformation rules define:</t>
+          <t>Series index default:</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>0-based</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Conversion logic</t>
+          <t>1-based</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>Random</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -948,39 +888,34 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data enrichment means:</t>
+          <t>DataFrame stores:</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Delete</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Add value</t>
+          <t>Lists</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Copy</t>
+          <t>Sets</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -990,39 +925,34 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Easy</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Error handling is for:</t>
+          <t>Rows accessed by:</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ignore errors</t>
+          <t>loc/iloc</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Manage failures</t>
+          <t>dtype</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Speed</t>
+          <t>shape</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1032,207 +962,142 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Easy</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A company ingests social media posts (text, emojis), cleans noise, extracts entities, and stores features for analytics. Which phase performs entity extraction?</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Extract</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Transform</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Load</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>Define Series.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>One Word</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Server logs are continuously collected and processed in near real-time to detect anomalies. Which ETL type?</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Batch</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Streaming</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>Define DataFrame.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>One Word</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Images are converted into embeddings and normalized before storage. Which phase?</t>
+          <t>Access row using label. Which?</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Extract</t>
+          <t>iloc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Transform</t>
+          <t>loc</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Load</t>
+          <t>head</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>tail</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>Scenario</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Raw CSVs are read from S3 and pushed into staging without changes. Which phase?</t>
+          <t>Access row using index number. Which?</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Extract</t>
+          <t>loc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Transform</t>
+          <t>iloc</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Load</t>
+          <t>describe</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>info</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Option A</t>
+          <t>Scenario</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>After cleaning and validation, curated data is written to warehouse tables. Which phase?</t>
+          <t>Count unique values in column. Method?</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Extract</t>
+          <t>count</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Transform</t>
+          <t>value_counts</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Load</t>
+          <t>sum</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1242,59 +1107,49 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Option C</t>
+          <t>Scenario</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A pipeline retries failed records and logs errors for auditing. Which concept?</t>
+          <t>Get statistical summary. Method?</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Caching</t>
+          <t>info</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Error handling</t>
+          <t>describe</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Indexing</t>
+          <t>head</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sharding</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>Scenario</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
